--- a/backend/app/services/brim_providers/sample_reports/credit_agricole-conti.xlsx
+++ b/backend/app/services/brim_providers/sample_reports/credit_agricole-conti.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimenti" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,100 +413,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Lista Movimenti Conto</t>
+          <t>Data Op.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Data Val.</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Causale</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Descrizione</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Importo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Divisa</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Saldo Iniziale 2984,99 EUR</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PAGAMENTO UTENZE</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Saldo Finale 58822,00 EUR</t>
+          <t>SDD A : UTILITY PROVIDER ADDEBITO SDD NUMERO 0000000001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>'-61,20</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data dal 01/07/2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PRELIEVO SPORT. AUTOM. ALTRA BANCA</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Data al 31/07/2026</t>
+          <t>PREL. CON CARTA 00000000 DEL 29/07/26 ALTRA BANCA -SPORT. ROMA</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>'-500,00</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28/07/2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PAGAMENTO TRAMITE POS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>POS CARTA 00000000 DEL 28/07/26 C/O SUPERMARKET - ROMA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>'-42,10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Op.</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Data Val.</t>
+          <t>01/07/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Causale</t>
+          <t>ACCREDITO EMOLUMENTI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Descrizione</t>
+          <t>PENSIONE INPS 0000 000 00000000 01 DEL 01.07.2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Importo</t>
+          <t>2879,70</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Divisa</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>05/07/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PAGAMENTO UTENZE</t>
+          <t>GIROCONTO/BONIFICO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SDD A : UTILITY PROVIDER ADDEBITO SDD NUMERO 0000000001</t>
+          <t>ORD:MITTENTE SAMPLE DT.ORD:000000 DESCR.OPERAZIONE SCT:RIMBORSO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-61,20</t>
+          <t>231,00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -518,27 +611,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PRELIEVO SPORT. AUTOM. ALTRA BANCA</t>
+          <t>CEDOLE, DIVIDENDI, PREMI ESTRATTI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PREL. CON CARTA 00000000 DEL 29/07/26 ALTRA BANCA -SPORT. ROMA</t>
+          <t>CEDOLA:BTP SAMPLE 1/12/2026 IT0000000001 DOS:00000/00000000 NOMINALE: 40.000,00 TASSO: 1,25 ALIQ: 12,50 RITENUTA: 31,25 DATA : 01/06/2026 N.MOVIM: 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-500,00</t>
+          <t>218,75</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -550,27 +643,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PAGAMENTO TRAMITE POS</t>
+          <t>CEDOLE, DIVIDENDI, PREMI ESTRATTI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>POS CARTA 00000000 DEL 28/07/26 C/O SUPERMARKET - ROMA</t>
+          <t>DIVIDENDO AZIONE SAMPLE IT0000000002 DOS:00000/00000000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-42,10</t>
+          <t>95,40</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -582,27 +675,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ACCREDITO EMOLUMENTI</t>
+          <t>CEDOLE, DIVIDENDI, PREMI ESTRATTI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PENSIONE INPS 0000 000 00000000 01 DEL 01.07.2026</t>
+          <t>DIVIDENDO CONGUAGLIO SENZA TITOLO IDENTIFICATO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2879,70</t>
+          <t>12,00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -614,27 +707,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIROCONTO/BONIFICO</t>
+          <t>COMMISS./SPESE SU OPERAZ. TITOLI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ORD:MITTENTE SAMPLE DT.ORD:000000 DESCR.OPERAZIONE SCT:RIMBORSO</t>
+          <t>ADDEBITO CAPITAL GAIN (D.LGS 461/97) 0000000000000 DATA:21/05/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>231,00</t>
+          <t>'-21,42</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -656,17 +749,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CEDOLE, DIVIDENDI, PREMI ESTRATTI</t>
+          <t>COMMISS./SPESE SU OPERAZ. TITOLI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CEDOLA:BTP SAMPLE 1/12/2026 IT0000000001 DOS:00000/00000000 NOMINALE: 40.000,00 TASSO: 1,25</t>
+          <t>SPESE STACCO CEDOLA DEL 01/06/2026 DOSSIER: 00000/00000000 TIT: IT0000000001</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>218,75</t>
+          <t>'-1,50</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -678,27 +771,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CEDOLE, DIVIDENDI, PREMI ESTRATTI</t>
+          <t>COMMISSIONI/SPESE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DIVIDENDO AZIONE SAMPLE IT0000000002 DOS:00000/00000000</t>
+          <t>Imposta bollo prodotti finanziari DATA 30/06/2026 RAPP.00000/0000000000000 TIT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>95,40</t>
+          <t>'-87,50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -710,27 +803,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CEDOLE, DIVIDENDI, PREMI ESTRATTI</t>
+          <t>COMMISSIONI/SPESE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DIVIDENDO CONGUAGLIO SENZA TITOLO IDENTIFICATO</t>
+          <t>SPESE DI GESTIONE E AMMINISTRAZ. DOS:0000/00000000 DATA:30/06/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12,00</t>
+          <t>'-10,00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -742,7 +835,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -752,17 +845,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COMMISS./SPESE SU OPERAZ. TITOLI</t>
+          <t>INTERESSI/COMPETENZE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ADDEBITO CAPITAL GAIN (D.LGS 461/97) 0000000000000 DATA:21/05/2026</t>
+          <t>CANONE MENSILE CONTO SMART 06/26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-21,42</t>
+          <t>'-4,00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -774,27 +867,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>31/12/2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>31/12/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COMMISS./SPESE SU OPERAZ. TITOLI</t>
+          <t>INTERESSI/COMPETENZE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SPESE STACCO CEDOLA DEL 01/06/2026 DOSSIER: 00000/00000000 TIT: IT0000000001</t>
+          <t>INTERESSI CREDITORI LORDI ANNO 2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-1,50</t>
+          <t>3,20</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -806,27 +899,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COMMISSIONI/SPESE</t>
+          <t>COMPRAVENDITA TITOLI/FONDI/OPZIONI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Imposta bollo prodotti finanziari DATA 30/06/2026 RAPP.00000/0000000000000 TIT</t>
+          <t>NOTA INF. ACQ. TIT:BTP SAMPLE DOSS:00000/00000000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-87,50</t>
+          <t>'-40.000,00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -838,27 +931,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COMMISSIONI/SPESE</t>
+          <t>CEDOLE, DIVIDENDI, PREMI ESTRATTI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SPESE DI GESTIONE E AMMINISTRAZ. DOS:0000/00000000 DATA:30/06/2026</t>
+          <t>CEDOLA:BTP OTHER 1/9/2030 IT0000000003 DOS:00000/00000000 NOMINALE: 20.000,00 TASSO: 2,00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-10,00</t>
+          <t>200,00</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -870,27 +963,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>INTERESSI/COMPETENZE</t>
+          <t>COMPRAVENDITA TITOLI/FONDI/OPZIONI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CANONE MENSILE CONTO SMART 06/26</t>
+          <t>NOTA INF. ACQ. TIT:BTP OTHER 1/9/2030 DOSS:00000/00000000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-4,00</t>
+          <t>'-20.412,33</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -902,27 +995,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>31/12/2025</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>31/12/2025</t>
+          <t>20/07/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>INTERESSI/COMPETENZE</t>
+          <t>COMPRAVENDITA TITOLI/FONDI/OPZIONI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>INTERESSI CREDITORI LORDI ANNO 2025</t>
+          <t>NOTA INF. VEND. TIT:BTP OTHER 1/9/2030 DOSS:00000/00000000</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3,20</t>
+          <t>20.180,00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -934,12 +1027,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -949,12 +1042,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NOTA INF. ACQ. TIT:BTP SAMPLE DOSS:00000/00000000</t>
+          <t>SOTTOSC SICAV ORD.:2026/000000001 SAMPLE GLOB EQ FUND</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-15.000,00</t>
+          <t>'-5.000,00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1050,10 +1143,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-50,00</t>
+          <t>'-50,00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>11/11/2025</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GIROCONTO/BONIFICO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ORD:SAMPLE FUND SICAV DT.ORD:000000 DESCR.OPERAZIONESCT::RIMBORSI: : : :SU SAMPLE FUND SIC AV CL B&lt;*&gt; RIFERIMENTO SCT:XX-2025-11-10-000000001 IDENTIFICATIVO SCT:</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9.984,47</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
